--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260814.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260814.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>76,207</t>
+          <t>75,207</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.47%</t>
+          <t>11.19%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>31,596</t>
+          <t>30,996</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.75%</t>
+          <t>10.86%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>88,425</t>
+          <t>86,925</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>8.42%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>34,755</t>
+          <t>34,155</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.71%</t>
+          <t>7.72%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>191,056</t>
+          <t>187,756</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.36%</t>
+          <t>5.33%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>101,591</t>
+          <t>99,791</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>4.08%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>47,895</t>
+          <t>47,095</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>110,166</t>
+          <t>108,266</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>57,659</t>
+          <t>56,759</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>18,979</t>
+          <t>18,679</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>114,583</t>
+          <t>112,583</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>53,027</t>
+          <t>52,127</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>22,031</t>
+          <t>21,631</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>133,501</t>
+          <t>131,101</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,804</t>
+          <t>23,404</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>61,003</t>
+          <t>59,903</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>35,980</t>
+          <t>35,380</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -985,29 +985,29 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>48,636</t>
+          <t>47,836</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>75,401</t>
+          <t>49,210</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,44 +1019,44 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>48,960</t>
+          <t>74,101</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>50,110</t>
+          <t>48,160</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>31,810</t>
+          <t>31,310</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1095,34 +1095,34 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>93,063</t>
+          <t>91,463</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>29,745</t>
+          <t>10,937</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1139,78 +1139,78 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,758</t>
+          <t>21,458</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>11,037</t>
+          <t>29,245</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>8,804</t>
+          <t>26,469</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>26,969</t>
+          <t>8,704</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>46,027</t>
+          <t>45,227</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>20,209</t>
+          <t>19,909</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>4,821</t>
+          <t>4,721</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,78 +1293,78 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>73,474</t>
+          <t>72,174</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>142,945</t>
+          <t>12,752</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>29,614</t>
+          <t>140,345</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>12,952</t>
+          <t>29,114</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>10,346</t>
+          <t>10,246</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>29,991</t>
+          <t>29,491</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,181</t>
+          <t>24,781</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>42,583</t>
+          <t>41,783</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,124</t>
+          <t>12,924</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>15,727</t>
+          <t>15,527</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1535,56 +1535,56 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,627</t>
+          <t>6,527</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>92,502</t>
+          <t>5,678</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,778</t>
+          <t>90,902</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,019</t>
+          <t>22,619</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>7,821</t>
+          <t>7,721</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,053</t>
+          <t>17,753</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>37,461</t>
+          <t>36,761</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>133,541,458</t>
+          <t>149,115,416</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
